--- a/partial/sliding_window_results_window_4.xlsx
+++ b/partial/sliding_window_results_window_4.xlsx
@@ -463,13 +463,13 @@
         <v>29.37</v>
       </c>
       <c r="C2" t="n">
-        <v>28.89001476677979</v>
+        <v>29.93040638646515</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.4799852332202157</v>
+        <v>0.5604063864651536</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2303858241094648</v>
+        <v>0.3140553179909311</v>
       </c>
     </row>
     <row r="3">
@@ -480,13 +480,13 @@
         <v>29.54</v>
       </c>
       <c r="C3" t="n">
-        <v>28.75143858845029</v>
+        <v>29.32506259951632</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.7885614115497042</v>
+        <v>-0.2149374004836773</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6218290997852619</v>
+        <v>0.04619808612668067</v>
       </c>
     </row>
     <row r="4">
@@ -497,13 +497,13 @@
         <v>29.55</v>
       </c>
       <c r="C4" t="n">
-        <v>29.89835923284729</v>
+        <v>29.77535200065974</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3483592328472938</v>
+        <v>0.2253520006597398</v>
       </c>
       <c r="E4" t="n">
-        <v>0.121354155109955</v>
+        <v>0.05078352420134737</v>
       </c>
     </row>
     <row r="5">
@@ -514,13 +514,13 @@
         <v>29.75</v>
       </c>
       <c r="C5" t="n">
-        <v>29.63077792719183</v>
+        <v>29.6515993714725</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1192220728081672</v>
+        <v>-0.09840062852750009</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01421390264467592</v>
+        <v>0.009682683694607064</v>
       </c>
     </row>
     <row r="6">
@@ -531,13 +531,13 @@
         <v>29.84</v>
       </c>
       <c r="C6" t="n">
-        <v>30.5128942614997</v>
+        <v>30.2031358527179</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6728942614997031</v>
+        <v>0.3631358527178961</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4527866871592308</v>
+        <v>0.1318676475291535</v>
       </c>
     </row>
     <row r="7">
@@ -548,13 +548,13 @@
         <v>29.81</v>
       </c>
       <c r="C7" t="n">
-        <v>30.38213655779985</v>
+        <v>30.08469355855535</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5721365577998547</v>
+        <v>0.2746935585553487</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3273402407710665</v>
+        <v>0.07545655111180079</v>
       </c>
     </row>
     <row r="8">
@@ -565,13 +565,13 @@
         <v>29.92</v>
       </c>
       <c r="C8" t="n">
-        <v>30.20936628021572</v>
+        <v>29.83023722208232</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2893662802157166</v>
+        <v>-0.08976277791768439</v>
       </c>
       <c r="E8" t="n">
-        <v>0.08373284412588064</v>
+        <v>0.008057356299499528</v>
       </c>
     </row>
     <row r="9">
@@ -582,13 +582,13 @@
         <v>29.98</v>
       </c>
       <c r="C9" t="n">
-        <v>29.55296524203012</v>
+        <v>29.75417165550755</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4270347579698814</v>
+        <v>-0.2258283444924487</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1823586845143952</v>
+        <v>0.05099844117620009</v>
       </c>
     </row>
     <row r="10">
@@ -599,13 +599,13 @@
         <v>30.04</v>
       </c>
       <c r="C10" t="n">
-        <v>29.82614341319439</v>
+        <v>29.76025260776232</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2138565868056048</v>
+        <v>-0.279747392237681</v>
       </c>
       <c r="E10" t="n">
-        <v>0.04573463972014319</v>
+        <v>0.07825860346378292</v>
       </c>
     </row>
     <row r="11">
@@ -616,13 +616,13 @@
         <v>30.21</v>
       </c>
       <c r="C11" t="n">
-        <v>29.36463635328873</v>
+        <v>29.83803663878533</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.8453636467112702</v>
+        <v>-0.371963361214668</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7146396951809773</v>
+        <v>0.1383567420861136</v>
       </c>
     </row>
     <row r="12">
@@ -633,13 +633,13 @@
         <v>30.22</v>
       </c>
       <c r="C12" t="n">
-        <v>29.76049113547246</v>
+        <v>30.01462314165534</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.4595088645275425</v>
+        <v>-0.2053768583446605</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2111483965793914</v>
+        <v>0.04217965394352273</v>
       </c>
     </row>
     <row r="13">
@@ -650,13 +650,13 @@
         <v>30.38</v>
       </c>
       <c r="C13" t="n">
-        <v>29.57582474233583</v>
+        <v>30.31141795601553</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.8041752576641734</v>
+        <v>-0.06858204398446688</v>
       </c>
       <c r="E13" t="n">
-        <v>0.6466978450392397</v>
+        <v>0.004703496757087349</v>
       </c>
     </row>
     <row r="14">
@@ -667,13 +667,13 @@
         <v>30.44</v>
       </c>
       <c r="C14" t="n">
-        <v>30.25487101437291</v>
+        <v>30.57077553773555</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1851289856270917</v>
+        <v>0.1307755377355484</v>
       </c>
       <c r="E14" t="n">
-        <v>0.03427274131931592</v>
+        <v>0.01710224127002184</v>
       </c>
     </row>
     <row r="15">
@@ -684,13 +684,13 @@
         <v>30.48</v>
       </c>
       <c r="C15" t="n">
-        <v>30.24752593861029</v>
+        <v>30.32483362114042</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2324740613897056</v>
+        <v>-0.1551663788595832</v>
       </c>
       <c r="E15" t="n">
-        <v>0.05404418921902461</v>
+        <v>0.0240766051283957</v>
       </c>
     </row>
     <row r="16">
@@ -701,13 +701,13 @@
         <v>30.69</v>
       </c>
       <c r="C16" t="n">
-        <v>30.50795299579393</v>
+        <v>30.35613061192455</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1820470042060691</v>
+        <v>-0.3338693880754562</v>
       </c>
       <c r="E16" t="n">
-        <v>0.03314111174040454</v>
+        <v>0.1114687682938796</v>
       </c>
     </row>
     <row r="17">
@@ -718,13 +718,13 @@
         <v>30.75</v>
       </c>
       <c r="C17" t="n">
-        <v>30.14916819334217</v>
+        <v>30.87410749143421</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6008318066578333</v>
+        <v>0.1241074914342057</v>
       </c>
       <c r="E17" t="n">
-        <v>0.360998859891716</v>
+        <v>0.01540266943009145</v>
       </c>
     </row>
     <row r="18">
@@ -735,13 +735,13 @@
         <v>30.94</v>
       </c>
       <c r="C18" t="n">
-        <v>30.54755445311316</v>
+        <v>30.7632536985891</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3924455468868437</v>
+        <v>-0.1767463014108976</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1540135072713139</v>
+        <v>0.03123925506243188</v>
       </c>
     </row>
     <row r="19">
@@ -752,13 +752,13 @@
         <v>30.95</v>
       </c>
       <c r="C19" t="n">
-        <v>30.83058250184288</v>
+        <v>30.89930378231916</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1194174981571194</v>
+        <v>-0.05069621768083721</v>
       </c>
       <c r="E19" t="n">
-        <v>0.01426053886610562</v>
+        <v>0.002570106487142831</v>
       </c>
     </row>
     <row r="20">
@@ -769,13 +769,13 @@
         <v>31.02</v>
       </c>
       <c r="C20" t="n">
-        <v>31.44412689269855</v>
+        <v>31.13777421556491</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4241268926985455</v>
+        <v>0.1177742155649142</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1798836211101235</v>
+        <v>0.01387076585193087</v>
       </c>
     </row>
     <row r="21">
@@ -786,13 +786,13 @@
         <v>31.12</v>
       </c>
       <c r="C21" t="n">
-        <v>31.82781453430661</v>
+        <v>31.28926585984339</v>
       </c>
       <c r="D21" t="n">
-        <v>0.7078145343066069</v>
+        <v>0.1692658598433923</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5010014149756788</v>
+        <v>0.02865093130852291</v>
       </c>
     </row>
     <row r="22">
@@ -803,13 +803,13 @@
         <v>31.28</v>
       </c>
       <c r="C22" t="n">
-        <v>31.96328579171908</v>
+        <v>31.19905793677455</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6832857917190793</v>
+        <v>-0.08094206322545361</v>
       </c>
       <c r="E22" t="n">
-        <v>0.466879473165169</v>
+        <v>0.00655161759919333</v>
       </c>
     </row>
     <row r="23">
@@ -820,13 +820,13 @@
         <v>31.38</v>
       </c>
       <c r="C23" t="n">
-        <v>31.78113201892211</v>
+        <v>31.11989792002061</v>
       </c>
       <c r="D23" t="n">
-        <v>0.4011320189221124</v>
+        <v>-0.2601020799793901</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1609068966045299</v>
+        <v>0.06765309200960502</v>
       </c>
     </row>
     <row r="24">
@@ -837,13 +837,13 @@
         <v>31.58</v>
       </c>
       <c r="C24" t="n">
-        <v>32.160315343314</v>
+        <v>31.32230849825455</v>
       </c>
       <c r="D24" t="n">
-        <v>0.5803153433140054</v>
+        <v>-0.2576915017454482</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3367658976856519</v>
+        <v>0.06640491007182434</v>
       </c>
     </row>
     <row r="25">
@@ -854,13 +854,13 @@
         <v>31.65</v>
       </c>
       <c r="C25" t="n">
-        <v>32.00960149047535</v>
+        <v>31.78016681862083</v>
       </c>
       <c r="D25" t="n">
-        <v>0.3596014904753559</v>
+        <v>0.130166818620836</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1293132319520975</v>
+        <v>0.01694340066986962</v>
       </c>
     </row>
     <row r="26">
@@ -871,13 +871,13 @@
         <v>31.88</v>
       </c>
       <c r="C26" t="n">
-        <v>32.63924261539053</v>
+        <v>32.52623230257632</v>
       </c>
       <c r="D26" t="n">
-        <v>0.7592426153905301</v>
+        <v>0.646232302576319</v>
       </c>
       <c r="E26" t="n">
-        <v>0.5764493490250524</v>
+        <v>0.4176161888930912</v>
       </c>
     </row>
     <row r="27">
@@ -888,13 +888,13 @@
         <v>32.28</v>
       </c>
       <c r="C27" t="n">
-        <v>32.54260657892653</v>
+        <v>32.57684602740945</v>
       </c>
       <c r="D27" t="n">
-        <v>0.2626065789265297</v>
+        <v>0.296846027409444</v>
       </c>
       <c r="E27" t="n">
-        <v>0.06896221529549569</v>
+        <v>0.08811756398876837</v>
       </c>
     </row>
     <row r="28">
@@ -905,13 +905,13 @@
         <v>32.45</v>
       </c>
       <c r="C28" t="n">
-        <v>32.63701460952016</v>
+        <v>32.91880862076341</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1870146095201619</v>
+        <v>0.4688086207634043</v>
       </c>
       <c r="E28" t="n">
-        <v>0.03497446417397863</v>
+        <v>0.2197815229020855</v>
       </c>
     </row>
     <row r="29">
@@ -922,13 +922,13 @@
         <v>32.85</v>
       </c>
       <c r="C29" t="n">
-        <v>32.90057566603382</v>
+        <v>33.19745864027098</v>
       </c>
       <c r="D29" t="n">
-        <v>0.05057566603382213</v>
+        <v>0.3474586402709789</v>
       </c>
       <c r="E29" t="n">
-        <v>0.00255789799476471</v>
+        <v>0.1207275066989576</v>
       </c>
     </row>
     <row r="30">
@@ -939,13 +939,13 @@
         <v>32.9</v>
       </c>
       <c r="C30" t="n">
-        <v>33.03819570847567</v>
+        <v>33.25509844645786</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1381957084756706</v>
+        <v>0.3550984464578661</v>
       </c>
       <c r="E30" t="n">
-        <v>0.01909805384109255</v>
+        <v>0.12609490667679</v>
       </c>
     </row>
     <row r="31">
@@ -956,13 +956,13 @@
         <v>33.1</v>
       </c>
       <c r="C31" t="n">
-        <v>33.09098749567925</v>
+        <v>33.33737814353816</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.009012504320750736</v>
+        <v>0.2373781435381588</v>
       </c>
       <c r="E31" t="n">
-        <v>8.122523413155069e-05</v>
+        <v>0.05634838302962272</v>
       </c>
     </row>
     <row r="32">
@@ -973,13 +973,13 @@
         <v>33.4</v>
       </c>
       <c r="C32" t="n">
-        <v>33.90732008781475</v>
+        <v>33.74769882878559</v>
       </c>
       <c r="D32" t="n">
-        <v>0.5073200878147475</v>
+        <v>0.3476988287855889</v>
       </c>
       <c r="E32" t="n">
-        <v>0.2573736715003631</v>
+        <v>0.1208944755388703</v>
       </c>
     </row>
     <row r="33">
@@ -990,13 +990,13 @@
         <v>33.7</v>
       </c>
       <c r="C33" t="n">
-        <v>33.87702641505651</v>
+        <v>33.74683683692324</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1770264150565097</v>
+        <v>0.04683683692324081</v>
       </c>
       <c r="E33" t="n">
-        <v>0.03133835162775966</v>
+        <v>0.002193689292974254</v>
       </c>
     </row>
     <row r="34">
@@ -1007,13 +1007,13 @@
         <v>34.1</v>
       </c>
       <c r="C34" t="n">
-        <v>34.03465604421379</v>
+        <v>33.81645724358367</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.06534395578621144</v>
+        <v>-0.2835427564163311</v>
       </c>
       <c r="E34" t="n">
-        <v>0.004269832557790355</v>
+        <v>0.08039649471617086</v>
       </c>
     </row>
     <row r="35">
@@ -1024,13 +1024,13 @@
         <v>34.4</v>
       </c>
       <c r="C35" t="n">
-        <v>34.22302632320909</v>
+        <v>34.20987557560572</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.176973676790908</v>
+        <v>-0.190124424394277</v>
       </c>
       <c r="E35" t="n">
-        <v>0.03131968227689278</v>
+        <v>0.03614729675125516</v>
       </c>
     </row>
     <row r="36">
@@ -1041,13 +1041,13 @@
         <v>34.9</v>
       </c>
       <c r="C36" t="n">
-        <v>34.82030886764005</v>
+        <v>34.42951112912753</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.0796911323599474</v>
+        <v>-0.4704888708724653</v>
       </c>
       <c r="E36" t="n">
-        <v>0.006350676576810656</v>
+        <v>0.2213597776148473</v>
       </c>
     </row>
     <row r="37">
@@ -1058,13 +1058,13 @@
         <v>35.3</v>
       </c>
       <c r="C37" t="n">
-        <v>35.83708905116644</v>
+        <v>35.46831273599246</v>
       </c>
       <c r="D37" t="n">
-        <v>0.5370890511664399</v>
+        <v>0.1683127359924583</v>
       </c>
       <c r="E37" t="n">
-        <v>0.2884646488828667</v>
+        <v>0.02832917709726698</v>
       </c>
     </row>
     <row r="38">
@@ -1075,13 +1075,13 @@
         <v>35.7</v>
       </c>
       <c r="C38" t="n">
-        <v>36.2456970187278</v>
+        <v>35.73577698497842</v>
       </c>
       <c r="D38" t="n">
-        <v>0.5456970187277932</v>
+        <v>0.03577698497841908</v>
       </c>
       <c r="E38" t="n">
-        <v>0.2977852362484015</v>
+        <v>0.001279992654146024</v>
       </c>
     </row>
     <row r="39">
@@ -1092,13 +1092,13 @@
         <v>36.3</v>
       </c>
       <c r="C39" t="n">
-        <v>36.50749343515574</v>
+        <v>36.01183120736154</v>
       </c>
       <c r="D39" t="n">
-        <v>0.2074934351557403</v>
+        <v>-0.2881687926384586</v>
       </c>
       <c r="E39" t="n">
-        <v>0.04305352563272938</v>
+        <v>0.08304125305070696</v>
       </c>
     </row>
     <row r="40">
@@ -1109,13 +1109,13 @@
         <v>36.8</v>
       </c>
       <c r="C40" t="n">
-        <v>37.04373366181021</v>
+        <v>36.63353645952962</v>
       </c>
       <c r="D40" t="n">
-        <v>0.2437336618102108</v>
+        <v>-0.1664635404703745</v>
       </c>
       <c r="E40" t="n">
-        <v>0.05940609789941423</v>
+        <v>0.027710110305932</v>
       </c>
     </row>
     <row r="41">
@@ -1126,13 +1126,13 @@
         <v>37.3</v>
       </c>
       <c r="C41" t="n">
-        <v>37.11686272164241</v>
+        <v>36.72230890903101</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.1831372783575915</v>
+        <v>-0.5776910909689903</v>
       </c>
       <c r="E41" t="n">
-        <v>0.03353926272422596</v>
+        <v>0.3337269965849422</v>
       </c>
     </row>
     <row r="42">
@@ -1143,13 +1143,13 @@
         <v>37.9</v>
       </c>
       <c r="C42" t="n">
-        <v>37.91988778998029</v>
+        <v>37.82487224815392</v>
       </c>
       <c r="D42" t="n">
-        <v>0.01988778998029517</v>
+        <v>-0.07512775184607534</v>
       </c>
       <c r="E42" t="n">
-        <v>0.0003955241903003288</v>
+        <v>0.005644179097445477</v>
       </c>
     </row>
     <row r="43">
@@ -1160,13 +1160,13 @@
         <v>38.5</v>
       </c>
       <c r="C43" t="n">
-        <v>38.46681989058308</v>
+        <v>38.59315908521873</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.03318010941691796</v>
+        <v>0.09315908521872984</v>
       </c>
       <c r="E43" t="n">
-        <v>0.001100919660918648</v>
+        <v>0.00867861515879057</v>
       </c>
     </row>
     <row r="44">
@@ -1177,13 +1177,13 @@
         <v>38.9</v>
       </c>
       <c r="C44" t="n">
-        <v>38.82259872457563</v>
+        <v>39.04101527828282</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.07740127542436426</v>
+        <v>0.141015278282822</v>
       </c>
       <c r="E44" t="n">
-        <v>0.005990957437318294</v>
+        <v>0.01988530870918173</v>
       </c>
     </row>
     <row r="45">
@@ -1194,13 +1194,13 @@
         <v>39.4</v>
       </c>
       <c r="C45" t="n">
-        <v>39.21682565764348</v>
+        <v>39.44285168523187</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.1831743423565158</v>
+        <v>0.04285168523186655</v>
       </c>
       <c r="E45" t="n">
-        <v>0.03355283969774204</v>
+        <v>0.00183626692721097</v>
       </c>
     </row>
     <row r="46">
@@ -1211,13 +1211,13 @@
         <v>39.9</v>
       </c>
       <c r="C46" t="n">
-        <v>39.40256336554837</v>
+        <v>39.70063914821225</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.4974366344516312</v>
+        <v>-0.1993608517877519</v>
       </c>
       <c r="E46" t="n">
-        <v>0.2474432052945658</v>
+        <v>0.03974474922553797</v>
       </c>
     </row>
     <row r="47">
@@ -1228,13 +1228,13 @@
         <v>40.1</v>
       </c>
       <c r="C47" t="n">
-        <v>39.71756715083095</v>
+        <v>40.02057981949194</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.3824328491690494</v>
+        <v>-0.07942018050805899</v>
       </c>
       <c r="E47" t="n">
-        <v>0.1462548841235569</v>
+        <v>0.006307565071932674</v>
       </c>
     </row>
     <row r="48">
@@ -1245,13 +1245,13 @@
         <v>40.6</v>
       </c>
       <c r="C48" t="n">
-        <v>39.94794240855921</v>
+        <v>40.24804694129041</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.6520575914407871</v>
+        <v>-0.35195305870959</v>
       </c>
       <c r="E48" t="n">
-        <v>0.4251791025555605</v>
+        <v>0.1238709555350361</v>
       </c>
     </row>
     <row r="49">
@@ -1262,13 +1262,13 @@
         <v>40.9</v>
       </c>
       <c r="C49" t="n">
-        <v>40.25461080979261</v>
+        <v>40.5721519782377</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.6453891902073892</v>
+        <v>-0.3278480217622999</v>
       </c>
       <c r="E49" t="n">
-        <v>0.4165272068365495</v>
+        <v>0.1074843253734535</v>
       </c>
     </row>
     <row r="50">
@@ -1279,13 +1279,13 @@
         <v>41.2</v>
       </c>
       <c r="C50" t="n">
-        <v>41.20170555541303</v>
+        <v>41.70425954152643</v>
       </c>
       <c r="D50" t="n">
-        <v>0.001705555413025195</v>
+        <v>0.5042595415264302</v>
       </c>
       <c r="E50" t="n">
-        <v>2.908919266899543e-06</v>
+        <v>0.2542776852204455</v>
       </c>
     </row>
     <row r="51">
@@ -1296,13 +1296,13 @@
         <v>41.5</v>
       </c>
       <c r="C51" t="n">
-        <v>41.43320693910871</v>
+        <v>41.83056249333569</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.06679306089128545</v>
+        <v>0.330562493335691</v>
       </c>
       <c r="E51" t="n">
-        <v>0.004461312983226965</v>
+        <v>0.1092715620003088</v>
       </c>
     </row>
     <row r="52">
@@ -1313,11 +1313,11 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>-0.2254557378848219</v>
+        <v>0.277971294333927</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="n">
-        <v>9.11363655173159</v>
+        <v>3.993299015679407</v>
       </c>
     </row>
     <row r="53">
@@ -1330,7 +1330,7 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="n">
-        <v>0.1822727310346318</v>
+        <v>0.07986598031358813</v>
       </c>
     </row>
   </sheetData>

--- a/partial/sliding_window_results_window_4.xlsx
+++ b/partial/sliding_window_results_window_4.xlsx
@@ -463,13 +463,13 @@
         <v>29.37</v>
       </c>
       <c r="C2" t="n">
-        <v>29.93040638646515</v>
+        <v>29.27129745229424</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5604063864651536</v>
+        <v>-0.09870254770575926</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3140553179909311</v>
+        <v>0.009742192923607682</v>
       </c>
     </row>
     <row r="3">
@@ -480,13 +480,13 @@
         <v>29.54</v>
       </c>
       <c r="C3" t="n">
-        <v>29.32506259951632</v>
+        <v>28.89858732122602</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.2149374004836773</v>
+        <v>-0.6414126787739782</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04619808612668067</v>
+        <v>0.4114102244920106</v>
       </c>
     </row>
     <row r="4">
@@ -497,13 +497,13 @@
         <v>29.55</v>
       </c>
       <c r="C4" t="n">
-        <v>29.77535200065974</v>
+        <v>29.59119588035839</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2253520006597398</v>
+        <v>0.04119588035839072</v>
       </c>
       <c r="E4" t="n">
-        <v>0.05078352420134737</v>
+        <v>0.001697100558502843</v>
       </c>
     </row>
     <row r="5">
@@ -514,13 +514,13 @@
         <v>29.75</v>
       </c>
       <c r="C5" t="n">
-        <v>29.6515993714725</v>
+        <v>29.5408948682246</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.09840062852750009</v>
+        <v>-0.2091051317754022</v>
       </c>
       <c r="E5" t="n">
-        <v>0.009682683694607064</v>
+        <v>0.04372495613480833</v>
       </c>
     </row>
     <row r="6">
@@ -531,13 +531,13 @@
         <v>29.84</v>
       </c>
       <c r="C6" t="n">
-        <v>30.2031358527179</v>
+        <v>30.09391412341247</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3631358527178961</v>
+        <v>0.2539141234124678</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1318676475291535</v>
+        <v>0.06447238206832191</v>
       </c>
     </row>
     <row r="7">
@@ -548,13 +548,13 @@
         <v>29.81</v>
       </c>
       <c r="C7" t="n">
-        <v>30.08469355855535</v>
+        <v>29.96780793677505</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2746935585553487</v>
+        <v>0.1578079367750469</v>
       </c>
       <c r="E7" t="n">
-        <v>0.07545655111180079</v>
+        <v>0.0249033449091972</v>
       </c>
     </row>
     <row r="8">
@@ -565,13 +565,13 @@
         <v>29.92</v>
       </c>
       <c r="C8" t="n">
-        <v>29.83023722208232</v>
+        <v>29.92889086957018</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.08976277791768439</v>
+        <v>0.008890869570180371</v>
       </c>
       <c r="E8" t="n">
-        <v>0.008057356299499528</v>
+        <v>7.904756171395929e-05</v>
       </c>
     </row>
     <row r="9">
@@ -582,13 +582,13 @@
         <v>29.98</v>
       </c>
       <c r="C9" t="n">
-        <v>29.75417165550755</v>
+        <v>29.6601667817109</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2258283444924487</v>
+        <v>-0.3198332182890979</v>
       </c>
       <c r="E9" t="n">
-        <v>0.05099844117620009</v>
+        <v>0.1022932875211618</v>
       </c>
     </row>
     <row r="10">
@@ -599,13 +599,13 @@
         <v>30.04</v>
       </c>
       <c r="C10" t="n">
-        <v>29.76025260776232</v>
+        <v>29.90254722852846</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.279747392237681</v>
+        <v>-0.1374527714715441</v>
       </c>
       <c r="E10" t="n">
-        <v>0.07825860346378292</v>
+        <v>0.01889326438520853</v>
       </c>
     </row>
     <row r="11">
@@ -616,13 +616,13 @@
         <v>30.21</v>
       </c>
       <c r="C11" t="n">
-        <v>29.83803663878533</v>
+        <v>29.8172723094264</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.371963361214668</v>
+        <v>-0.3927276905736043</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1383567420861136</v>
+        <v>0.1542350389432767</v>
       </c>
     </row>
     <row r="12">
@@ -633,13 +633,13 @@
         <v>30.22</v>
       </c>
       <c r="C12" t="n">
-        <v>30.01462314165534</v>
+        <v>30.05223122253703</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.2053768583446605</v>
+        <v>-0.1677687774629675</v>
       </c>
       <c r="E12" t="n">
-        <v>0.04217965394352273</v>
+        <v>0.0281463626914187</v>
       </c>
     </row>
     <row r="13">
@@ -650,13 +650,13 @@
         <v>30.38</v>
       </c>
       <c r="C13" t="n">
-        <v>30.31141795601553</v>
+        <v>30.1234776137297</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.06858204398446688</v>
+        <v>-0.2565223862702943</v>
       </c>
       <c r="E13" t="n">
-        <v>0.004703496757087349</v>
+        <v>0.06580373465780609</v>
       </c>
     </row>
     <row r="14">
@@ -667,13 +667,13 @@
         <v>30.44</v>
       </c>
       <c r="C14" t="n">
-        <v>30.57077553773555</v>
+        <v>30.55749822907353</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1307755377355484</v>
+        <v>0.1174982290735258</v>
       </c>
       <c r="E14" t="n">
-        <v>0.01710224127002184</v>
+        <v>0.01380583383541474</v>
       </c>
     </row>
     <row r="15">
@@ -684,13 +684,13 @@
         <v>30.48</v>
       </c>
       <c r="C15" t="n">
-        <v>30.32483362114042</v>
+        <v>30.37855185485765</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1551663788595832</v>
+        <v>-0.1014481451423528</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0240766051283957</v>
+        <v>0.01029172615282388</v>
       </c>
     </row>
     <row r="16">
@@ -701,13 +701,13 @@
         <v>30.69</v>
       </c>
       <c r="C16" t="n">
-        <v>30.35613061192455</v>
+        <v>30.43747933059789</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3338693880754562</v>
+        <v>-0.2525206694021129</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1114687682938796</v>
+        <v>0.06376668847529121</v>
       </c>
     </row>
     <row r="17">
@@ -718,13 +718,13 @@
         <v>30.75</v>
       </c>
       <c r="C17" t="n">
-        <v>30.87410749143421</v>
+        <v>30.52653242292372</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1241074914342057</v>
+        <v>-0.2234675770762777</v>
       </c>
       <c r="E17" t="n">
-        <v>0.01540266943009145</v>
+        <v>0.04993775800434213</v>
       </c>
     </row>
     <row r="18">
@@ -735,13 +735,13 @@
         <v>30.94</v>
       </c>
       <c r="C18" t="n">
-        <v>30.7632536985891</v>
+        <v>30.58897057625037</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1767463014108976</v>
+        <v>-0.3510294237496332</v>
       </c>
       <c r="E18" t="n">
-        <v>0.03123925506243188</v>
+        <v>0.1232216563379995</v>
       </c>
     </row>
     <row r="19">
@@ -752,13 +752,13 @@
         <v>30.95</v>
       </c>
       <c r="C19" t="n">
-        <v>30.89930378231916</v>
+        <v>30.70311676668494</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.05069621768083721</v>
+        <v>-0.2468832333150637</v>
       </c>
       <c r="E19" t="n">
-        <v>0.002570106487142831</v>
+        <v>0.06095133089210017</v>
       </c>
     </row>
     <row r="20">
@@ -769,13 +769,13 @@
         <v>31.02</v>
       </c>
       <c r="C20" t="n">
-        <v>31.13777421556491</v>
+        <v>31.05489795694345</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1177742155649142</v>
+        <v>0.03489795694344977</v>
       </c>
       <c r="E20" t="n">
-        <v>0.01387076585193087</v>
+        <v>0.001217867398826874</v>
       </c>
     </row>
     <row r="21">
@@ -786,13 +786,13 @@
         <v>31.12</v>
       </c>
       <c r="C21" t="n">
-        <v>31.28926585984339</v>
+        <v>31.28787841519338</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1692658598433923</v>
+        <v>0.1678784151933819</v>
       </c>
       <c r="E21" t="n">
-        <v>0.02865093130852291</v>
+        <v>0.02818316228784151</v>
       </c>
     </row>
     <row r="22">
@@ -803,13 +803,13 @@
         <v>31.28</v>
       </c>
       <c r="C22" t="n">
-        <v>31.19905793677455</v>
+        <v>31.35561239598821</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.08094206322545361</v>
+        <v>0.0756123959882089</v>
       </c>
       <c r="E22" t="n">
-        <v>0.00655161759919333</v>
+        <v>0.00571723442707771</v>
       </c>
     </row>
     <row r="23">
@@ -820,13 +820,13 @@
         <v>31.38</v>
       </c>
       <c r="C23" t="n">
-        <v>31.11989792002061</v>
+        <v>31.34760380696315</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2601020799793901</v>
+        <v>-0.03239619303684904</v>
       </c>
       <c r="E23" t="n">
-        <v>0.06765309200960502</v>
+        <v>0.001049513323280786</v>
       </c>
     </row>
     <row r="24">
@@ -837,13 +837,13 @@
         <v>31.58</v>
       </c>
       <c r="C24" t="n">
-        <v>31.32230849825455</v>
+        <v>31.648838911214</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2576915017454482</v>
+        <v>0.06883891121400154</v>
       </c>
       <c r="E24" t="n">
-        <v>0.06640491007182434</v>
+        <v>0.004738795697129187</v>
       </c>
     </row>
     <row r="25">
@@ -854,13 +854,13 @@
         <v>31.65</v>
       </c>
       <c r="C25" t="n">
-        <v>31.78016681862083</v>
+        <v>31.53714669056195</v>
       </c>
       <c r="D25" t="n">
-        <v>0.130166818620836</v>
+        <v>-0.1128533094380444</v>
       </c>
       <c r="E25" t="n">
-        <v>0.01694340066986962</v>
+        <v>0.012735869451119</v>
       </c>
     </row>
     <row r="26">
@@ -871,13 +871,13 @@
         <v>31.88</v>
       </c>
       <c r="C26" t="n">
-        <v>32.52623230257632</v>
+        <v>32.07713100634141</v>
       </c>
       <c r="D26" t="n">
-        <v>0.646232302576319</v>
+        <v>0.1971310063414116</v>
       </c>
       <c r="E26" t="n">
-        <v>0.4176161888930912</v>
+        <v>0.03886063366117765</v>
       </c>
     </row>
     <row r="27">
@@ -888,13 +888,13 @@
         <v>32.28</v>
       </c>
       <c r="C27" t="n">
-        <v>32.57684602740945</v>
+        <v>31.98818124780108</v>
       </c>
       <c r="D27" t="n">
-        <v>0.296846027409444</v>
+        <v>-0.2918187521989211</v>
       </c>
       <c r="E27" t="n">
-        <v>0.08811756398876837</v>
+        <v>0.0851581841349353</v>
       </c>
     </row>
     <row r="28">
@@ -905,13 +905,13 @@
         <v>32.45</v>
       </c>
       <c r="C28" t="n">
-        <v>32.91880862076341</v>
+        <v>32.25530816121088</v>
       </c>
       <c r="D28" t="n">
-        <v>0.4688086207634043</v>
+        <v>-0.1946918387891259</v>
       </c>
       <c r="E28" t="n">
-        <v>0.2197815229020855</v>
+        <v>0.03790491209109098</v>
       </c>
     </row>
     <row r="29">
@@ -922,13 +922,13 @@
         <v>32.85</v>
       </c>
       <c r="C29" t="n">
-        <v>33.19745864027098</v>
+        <v>32.9297297073936</v>
       </c>
       <c r="D29" t="n">
-        <v>0.3474586402709789</v>
+        <v>0.07972970739359653</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1207275066989576</v>
+        <v>0.00635682624106852</v>
       </c>
     </row>
     <row r="30">
@@ -939,13 +939,13 @@
         <v>32.9</v>
       </c>
       <c r="C30" t="n">
-        <v>33.25509844645786</v>
+        <v>33.0825624823726</v>
       </c>
       <c r="D30" t="n">
-        <v>0.3550984464578661</v>
+        <v>0.1825624823726031</v>
       </c>
       <c r="E30" t="n">
-        <v>0.12609490667679</v>
+        <v>0.03332905997004701</v>
       </c>
     </row>
     <row r="31">
@@ -956,13 +956,13 @@
         <v>33.1</v>
       </c>
       <c r="C31" t="n">
-        <v>33.33737814353816</v>
+        <v>32.94691041913592</v>
       </c>
       <c r="D31" t="n">
-        <v>0.2373781435381588</v>
+        <v>-0.1530895808640764</v>
       </c>
       <c r="E31" t="n">
-        <v>0.05634838302962272</v>
+        <v>0.02343641976913859</v>
       </c>
     </row>
     <row r="32">
@@ -973,13 +973,13 @@
         <v>33.4</v>
       </c>
       <c r="C32" t="n">
-        <v>33.74769882878559</v>
+        <v>33.61080734333704</v>
       </c>
       <c r="D32" t="n">
-        <v>0.3476988287855889</v>
+        <v>0.210807343337045</v>
       </c>
       <c r="E32" t="n">
-        <v>0.1208944755388703</v>
+        <v>0.04443973600482276</v>
       </c>
     </row>
     <row r="33">
@@ -990,13 +990,13 @@
         <v>33.7</v>
       </c>
       <c r="C33" t="n">
-        <v>33.74683683692324</v>
+        <v>33.48260421731123</v>
       </c>
       <c r="D33" t="n">
-        <v>0.04683683692324081</v>
+        <v>-0.2173957826887687</v>
       </c>
       <c r="E33" t="n">
-        <v>0.002193689292974254</v>
+        <v>0.04726092633086234</v>
       </c>
     </row>
     <row r="34">
@@ -1007,13 +1007,13 @@
         <v>34.1</v>
       </c>
       <c r="C34" t="n">
-        <v>33.81645724358367</v>
+        <v>33.70847290520697</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.2835427564163311</v>
+        <v>-0.3915270947930267</v>
       </c>
       <c r="E34" t="n">
-        <v>0.08039649471617086</v>
+        <v>0.1532934659570677</v>
       </c>
     </row>
     <row r="35">
@@ -1024,13 +1024,13 @@
         <v>34.4</v>
       </c>
       <c r="C35" t="n">
-        <v>34.20987557560572</v>
+        <v>34.1268012502308</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.190124424394277</v>
+        <v>-0.2731987497692003</v>
       </c>
       <c r="E35" t="n">
-        <v>0.03614729675125516</v>
+        <v>0.07463755687545413</v>
       </c>
     </row>
     <row r="36">
@@ -1041,13 +1041,13 @@
         <v>34.9</v>
       </c>
       <c r="C36" t="n">
-        <v>34.42951112912753</v>
+        <v>34.75457724762305</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.4704888708724653</v>
+        <v>-0.1454227523769518</v>
       </c>
       <c r="E36" t="n">
-        <v>0.2213597776148473</v>
+        <v>0.02114777690888824</v>
       </c>
     </row>
     <row r="37">
@@ -1058,13 +1058,13 @@
         <v>35.3</v>
       </c>
       <c r="C37" t="n">
-        <v>35.46831273599246</v>
+        <v>35.48275448946125</v>
       </c>
       <c r="D37" t="n">
-        <v>0.1683127359924583</v>
+        <v>0.1827544894612529</v>
       </c>
       <c r="E37" t="n">
-        <v>0.02832917709726698</v>
+        <v>0.03339920341824321</v>
       </c>
     </row>
     <row r="38">
@@ -1075,13 +1075,13 @@
         <v>35.7</v>
       </c>
       <c r="C38" t="n">
-        <v>35.73577698497842</v>
+        <v>35.74086531239111</v>
       </c>
       <c r="D38" t="n">
-        <v>0.03577698497841908</v>
+        <v>0.04086531239110514</v>
       </c>
       <c r="E38" t="n">
-        <v>0.001279992654146024</v>
+        <v>0.001669973756822611</v>
       </c>
     </row>
     <row r="39">
@@ -1092,13 +1092,13 @@
         <v>36.3</v>
       </c>
       <c r="C39" t="n">
-        <v>36.01183120736154</v>
+        <v>36.2333328098435</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.2881687926384586</v>
+        <v>-0.06666719015650102</v>
       </c>
       <c r="E39" t="n">
-        <v>0.08304125305070696</v>
+        <v>0.004444514243363067</v>
       </c>
     </row>
     <row r="40">
@@ -1109,13 +1109,13 @@
         <v>36.8</v>
       </c>
       <c r="C40" t="n">
-        <v>36.63353645952962</v>
+        <v>36.70936325007804</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.1664635404703745</v>
+        <v>-0.09063674992195558</v>
       </c>
       <c r="E40" t="n">
-        <v>0.027710110305932</v>
+        <v>0.008215020436415116</v>
       </c>
     </row>
     <row r="41">
@@ -1126,13 +1126,13 @@
         <v>37.3</v>
       </c>
       <c r="C41" t="n">
-        <v>36.72230890903101</v>
+        <v>36.86839890316983</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.5776910909689903</v>
+        <v>-0.4316010968301711</v>
       </c>
       <c r="E41" t="n">
-        <v>0.3337269965849422</v>
+        <v>0.1862795067850067</v>
       </c>
     </row>
     <row r="42">
@@ -1143,13 +1143,13 @@
         <v>37.9</v>
       </c>
       <c r="C42" t="n">
-        <v>37.82487224815392</v>
+        <v>37.61664137484169</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.07512775184607534</v>
+        <v>-0.2833586251583071</v>
       </c>
       <c r="E42" t="n">
-        <v>0.005644179097445477</v>
+        <v>0.080292110451606</v>
       </c>
     </row>
     <row r="43">
@@ -1160,13 +1160,13 @@
         <v>38.5</v>
       </c>
       <c r="C43" t="n">
-        <v>38.59315908521873</v>
+        <v>38.42337260637814</v>
       </c>
       <c r="D43" t="n">
-        <v>0.09315908521872984</v>
+        <v>-0.07662739362186244</v>
       </c>
       <c r="E43" t="n">
-        <v>0.00867861515879057</v>
+        <v>0.005871757453279844</v>
       </c>
     </row>
     <row r="44">
@@ -1177,13 +1177,13 @@
         <v>38.9</v>
       </c>
       <c r="C44" t="n">
-        <v>39.04101527828282</v>
+        <v>38.88607338339919</v>
       </c>
       <c r="D44" t="n">
-        <v>0.141015278282822</v>
+        <v>-0.01392661660080563</v>
       </c>
       <c r="E44" t="n">
-        <v>0.01988530870918173</v>
+        <v>0.000193950649945835</v>
       </c>
     </row>
     <row r="45">
@@ -1194,13 +1194,13 @@
         <v>39.4</v>
       </c>
       <c r="C45" t="n">
-        <v>39.44285168523187</v>
+        <v>39.2989148143734</v>
       </c>
       <c r="D45" t="n">
-        <v>0.04285168523186655</v>
+        <v>-0.1010851856266015</v>
       </c>
       <c r="E45" t="n">
-        <v>0.00183626692721097</v>
+        <v>0.01021821475316449</v>
       </c>
     </row>
     <row r="46">
@@ -1211,13 +1211,13 @@
         <v>39.9</v>
       </c>
       <c r="C46" t="n">
-        <v>39.70063914821225</v>
+        <v>39.79755835293221</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.1993608517877519</v>
+        <v>-0.1024416470677849</v>
       </c>
       <c r="E46" t="n">
-        <v>0.03974474922553797</v>
+        <v>0.01049429105396061</v>
       </c>
     </row>
     <row r="47">
@@ -1228,13 +1228,13 @@
         <v>40.1</v>
       </c>
       <c r="C47" t="n">
-        <v>40.02057981949194</v>
+        <v>39.80929427432267</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.07942018050805899</v>
+        <v>-0.2907057256773271</v>
       </c>
       <c r="E47" t="n">
-        <v>0.006307565071932674</v>
+        <v>0.08450981894158137</v>
       </c>
     </row>
     <row r="48">
@@ -1245,13 +1245,13 @@
         <v>40.6</v>
       </c>
       <c r="C48" t="n">
-        <v>40.24804694129041</v>
+        <v>39.99342778975871</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.35195305870959</v>
+        <v>-0.6065722102412963</v>
       </c>
       <c r="E48" t="n">
-        <v>0.1238709555350361</v>
+        <v>0.3679298462370113</v>
       </c>
     </row>
     <row r="49">
@@ -1262,13 +1262,13 @@
         <v>40.9</v>
       </c>
       <c r="C49" t="n">
-        <v>40.5721519782377</v>
+        <v>40.30914263008578</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.3278480217622999</v>
+        <v>-0.5908573699142181</v>
       </c>
       <c r="E49" t="n">
-        <v>0.1074843253734535</v>
+        <v>0.3491124315819472</v>
       </c>
     </row>
     <row r="50">
@@ -1279,13 +1279,13 @@
         <v>41.2</v>
       </c>
       <c r="C50" t="n">
-        <v>41.70425954152643</v>
+        <v>41.75570030737111</v>
       </c>
       <c r="D50" t="n">
-        <v>0.5042595415264302</v>
+        <v>0.5557003073711115</v>
       </c>
       <c r="E50" t="n">
-        <v>0.2542776852204455</v>
+        <v>0.3088028316123478</v>
       </c>
     </row>
     <row r="51">
@@ -1296,13 +1296,13 @@
         <v>41.5</v>
       </c>
       <c r="C51" t="n">
-        <v>41.83056249333569</v>
+        <v>41.63490258777376</v>
       </c>
       <c r="D51" t="n">
-        <v>0.330562493335691</v>
+        <v>0.1349025877737589</v>
       </c>
       <c r="E51" t="n">
-        <v>0.1092715620003088</v>
+        <v>0.01819870818805671</v>
       </c>
     </row>
     <row r="52">
@@ -1313,11 +1313,11 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>0.277971294333927</v>
+        <v>-5.354760160809345</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="n">
-        <v>3.993299015679407</v>
+        <v>3.336476050637586</v>
       </c>
     </row>
     <row r="53">
@@ -1330,7 +1330,7 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="n">
-        <v>0.07986598031358813</v>
+        <v>0.06672952101275172</v>
       </c>
     </row>
   </sheetData>
